--- a/output/pdf_financials_xlsx/SDR.xlsx
+++ b/output/pdf_financials_xlsx/SDR.xlsx
@@ -6359,52 +6359,52 @@
         <v>1.609003</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.609003</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.932237</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.009023</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.029023</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.029023</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.050123</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.050123</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.100823</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.100823</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.577072</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.980054</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.003462</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.003462</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.243848</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.243848</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>4.233655</v>
       </c>
     </row>
     <row r="93">
@@ -10054,7 +10054,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10798,7 +10802,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11648,7 +11656,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12696,7 +12708,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13720,7 +13736,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14764,7 +14784,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -17496,7 +17520,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -20662,7 +20690,11 @@
           <t>Reserves 2,932,237</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SDR.xlsx
+++ b/output/pdf_financials_xlsx/SDR.xlsx
@@ -1212,25 +1212,25 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00116</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.014174</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.013068</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000893</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.009812</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.006535</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.000256</v>
       </c>
     </row>
     <row r="13">
@@ -2325,25 +2325,25 @@
         <v>-0.394133</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.869924</v>
+        <v>-0.871084</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.462452</v>
+        <v>-0.476626</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.450186</v>
+        <v>-3.463254</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.429883</v>
+        <v>-1.430776</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.27922</v>
+        <v>-0.289032</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.315737</v>
+        <v>-0.322272</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.381666</v>
+        <v>-0.381922</v>
       </c>
     </row>
     <row r="28">
@@ -2451,25 +2451,25 @@
         <v>-0.394133</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.869924</v>
+        <v>-0.871084</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.462452</v>
+        <v>-0.476626</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.450186</v>
+        <v>-3.463254</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.429883</v>
+        <v>-1.430776</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.27922</v>
+        <v>-0.289032</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.315737</v>
+        <v>-0.322272</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.381666</v>
+        <v>-0.381922</v>
       </c>
     </row>
     <row r="30">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -37112,7 +37112,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -38116,7 +38116,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -42384,7 +42384,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">

--- a/output/pdf_financials_xlsx/SDR.xlsx
+++ b/output/pdf_financials_xlsx/SDR.xlsx
@@ -851,10 +851,10 @@
         <v>0.023044</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.00463</v>
+        <v>0.03838</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.006002</v>
+        <v>0.051002</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.005697</v>
@@ -1500,7 +1500,7 @@
         <v>0.00478</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.04432</v>
+        <v>0.038291</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2584,7 +2584,7 @@
         <v>-2.647876713087602</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-5.56732163090366</v>
+        <v>-4.809979976735831</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -29904,7 +29904,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -35428,7 +35432,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -36170,7 +36178,11 @@
           <t>Future income taxes expense</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
         <v>0.372667</v>
       </c>
@@ -43804,7 +43816,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -47676,7 +47692,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
